--- a/finance/_refresh_qatar.xlsx
+++ b/finance/_refresh_qatar.xlsx
@@ -1313,7 +1313,7 @@
         </is>
       </c>
       <c r="B19" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>Cap on revenue sailings/day — ~1 sailing/70min in a 12h window; a believable on-demand premium duty cycle, not capacity-max (Jaideep 2026-06-19).</t>
+          <t>Cap on revenue sailings/day — MID headline duty cycle; thin=12 / full=18 bookends in _utilization_scenarios (Jaideep 2026-06-21).</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
         <v>0.45</v>
       </c>
       <c r="C31" s="19" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="F31" s="14" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>0.55</v>
       </c>
       <c r="C32" s="19" t="n">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>0.7</v>
       </c>
       <c r="C33" s="19" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v/>
       </c>
       <c r="K4" s="34">
-        <f>MIN(18,FLOOR(60*service_hr/J4,1))</f>
+        <f>MIN(27,FLOOR(60*service_hr/J4,1))</f>
         <v/>
       </c>
       <c r="L4" s="34">
@@ -2348,7 +2348,7 @@
         <v/>
       </c>
       <c r="K5" s="34">
-        <f>MIN(18,FLOOR(60*service_hr/J5,1))</f>
+        <f>MIN(27,FLOOR(60*service_hr/J5,1))</f>
         <v/>
       </c>
       <c r="L5" s="34">
@@ -2524,7 +2524,7 @@
         <v/>
       </c>
       <c r="K6" s="34">
-        <f>MIN(18,FLOOR(60*service_hr/J6,1))</f>
+        <f>MIN(27,FLOOR(60*service_hr/J6,1))</f>
         <v/>
       </c>
       <c r="L6" s="34">
@@ -2708,7 +2708,7 @@
         <v/>
       </c>
       <c r="K7" s="34">
-        <f>MIN(18,FLOOR(60*service_hr/J7,1))</f>
+        <f>MIN(27,FLOOR(60*service_hr/J7,1))</f>
         <v/>
       </c>
       <c r="L7" s="34">
@@ -2884,7 +2884,7 @@
         <v/>
       </c>
       <c r="K8" s="34">
-        <f>MIN(10,FLOOR(60*service_hr/J8,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J8,1))</f>
         <v/>
       </c>
       <c r="L8" s="34">
@@ -3078,7 +3078,7 @@
         <v/>
       </c>
       <c r="K9" s="34">
-        <f>MIN(18,FLOOR(60*service_hr/J9,1))</f>
+        <f>MIN(27,FLOOR(60*service_hr/J9,1))</f>
         <v/>
       </c>
       <c r="L9" s="34">
@@ -3266,7 +3266,7 @@
         <v/>
       </c>
       <c r="K10" s="34">
-        <f>MIN(18,FLOOR(60*service_hr/J10,1))</f>
+        <f>MIN(27,FLOOR(60*service_hr/J10,1))</f>
         <v/>
       </c>
       <c r="L10" s="34">
@@ -3432,7 +3432,7 @@
         <v/>
       </c>
       <c r="K11" s="34">
-        <f>MIN(18,FLOOR(60*service_hr/J11,1))</f>
+        <f>MIN(27,FLOOR(60*service_hr/J11,1))</f>
         <v/>
       </c>
       <c r="L11" s="34">
@@ -3598,7 +3598,7 @@
         <v/>
       </c>
       <c r="K12" s="34">
-        <f>MIN(18,FLOOR(60*service_hr/J12,1))</f>
+        <f>MIN(27,FLOOR(60*service_hr/J12,1))</f>
         <v/>
       </c>
       <c r="L12" s="34">
@@ -3952,13 +3952,13 @@
         </is>
       </c>
       <c r="B6" s="39" t="n">
-        <v>0.8581</v>
+        <v>0.8299</v>
       </c>
       <c r="C6" s="39" t="n">
-        <v>0.8581</v>
+        <v>0.8299</v>
       </c>
       <c r="D6" s="39" t="n">
-        <v>0.9081</v>
+        <v>0.8799</v>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
@@ -4030,11 +4030,11 @@
         </is>
       </c>
       <c r="C11" s="39" t="n">
-        <v>0.8581</v>
+        <v>0.8299</v>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Captive sole-operator capture (~86%) that builds the published floor; M_today = floor ÷ this = the true corridor spend pool.</t>
+          <t>Captive sole-operator capture (~83%) that builds the published floor; M_today = floor ÷ this = the true corridor spend pool.</t>
         </is>
       </c>
     </row>
@@ -4107,7 +4107,7 @@
     <row r="18">
       <c r="A18" s="25" t="inlineStr">
         <is>
-          <t>SOM full network (~86% capture, today, +greenfield)</t>
+          <t>SOM full network (~83% capture, today, +greenfield)</t>
         </is>
       </c>
       <c r="B18" s="50">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>Floor posture (~86% captive capture, today's demand) extended across the whole mapped network.</t>
+          <t>Floor posture (~83% captive capture, today's demand) extended across the whole mapped network.</t>
         </is>
       </c>
     </row>

--- a/finance/_refresh_qatar.xlsx
+++ b/finance/_refresh_qatar.xlsx
@@ -1332,7 +1332,7 @@
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>Cap on revenue sailings/day — MID headline duty cycle; thin=12 / full=18 bookends in _utilization_scenarios (Jaideep 2026-06-21).</t>
+          <t>Cap on revenue sailings/day — 15 across thin/mid/full scenarios (Jaideep 2026-06-21).</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
         <v>0.7</v>
       </c>
       <c r="C33" s="19" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>

--- a/finance/_refresh_qatar.xlsx
+++ b/finance/_refresh_qatar.xlsx
@@ -27,23 +27,23 @@
     <definedName name="dwell_min">'Assumptions'!$B$18</definedName>
     <definedName name="max_tpd">'Assumptions'!$B$19</definedName>
     <definedName name="crew_factor">'Assumptions'!$B$20</definedName>
-    <definedName name="ins_pct">'Assumptions'!$B$21</definedName>
-    <definedName name="charge_berth">'Assumptions'!$B$22</definedName>
-    <definedName name="mech_uptime">'Assumptions'!$B$23</definedName>
-    <definedName name="capture">'Assumptions'!$B$24</definedName>
-    <definedName name="capture_captive">'Assumptions'!$B$25</definedName>
-    <definedName name="discount">'Assumptions'!$B$26</definedName>
-    <definedName name="diesel_co2pg">'Assumptions'!$B$27</definedName>
-    <definedName name="load_thin">'Assumptions'!$B$31</definedName>
-    <definedName name="revleg_thin">'Assumptions'!$C$31</definedName>
-    <definedName name="load_mid">'Assumptions'!$B$32</definedName>
-    <definedName name="revleg_mid">'Assumptions'!$C$32</definedName>
-    <definedName name="load_full">'Assumptions'!$B$33</definedName>
-    <definedName name="revleg_full">'Assumptions'!$C$33</definedName>
-    <definedName name="band_tbl">'Assumptions'!$A$31:$C$33</definedName>
-    <definedName name="scenario">'Assumptions'!$B$35</definedName>
-    <definedName name="load_sel">'Assumptions'!$B$36</definedName>
-    <definedName name="revleg_sel">'Assumptions'!$B$37</definedName>
+    <definedName name="mech_uptime">'Assumptions'!$B$21</definedName>
+    <definedName name="capture">'Assumptions'!$B$22</definedName>
+    <definedName name="capture_captive">'Assumptions'!$B$23</definedName>
+    <definedName name="discount">'Assumptions'!$B$24</definedName>
+    <definedName name="diesel_co2pg">'Assumptions'!$B$25</definedName>
+    <definedName name="ins_pct">'Assumptions'!$B$29</definedName>
+    <definedName name="charge_berth">'Assumptions'!$B$30</definedName>
+    <definedName name="load_thin">'Assumptions'!$B$34</definedName>
+    <definedName name="revleg_thin">'Assumptions'!$C$34</definedName>
+    <definedName name="load_mid">'Assumptions'!$B$35</definedName>
+    <definedName name="revleg_mid">'Assumptions'!$C$35</definedName>
+    <definedName name="load_full">'Assumptions'!$B$36</definedName>
+    <definedName name="revleg_full">'Assumptions'!$C$36</definedName>
+    <definedName name="band_tbl">'Assumptions'!$A$34:$C$36</definedName>
+    <definedName name="scenario">'Assumptions'!$B$38</definedName>
+    <definedName name="load_sel">'Assumptions'!$B$39</definedName>
+    <definedName name="revleg_sel">'Assumptions'!$B$40</definedName>
     <definedName name="country_opex">'Country opex'!$A$4:$G$4</definedName>
     <definedName name="som_floor_fleet">'Corridor economics'!$D$18</definedName>
     <definedName name="som_floor_rev">'Corridor economics'!$E$18</definedName>
@@ -707,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B27"/>
+  <dimension ref="B2:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -786,84 +786,143 @@
     <row r="14">
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>EBITDA  = REVENUE − OPEX   (energy + captain + marina/overhead + maintenance)</t>
+          <t>EBITDA  = REVENUE − OPEX</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    OPEX = energy + crew + berth/port admin + maintenance + vessel insurance + fast-charge berth</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>PAYBACK = vessel CAPEX ÷ EBITDA</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="2" t="inlineStr"/>
-    </row>
     <row r="17">
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>From demand pool to fleet &amp; market size</t>
-        </is>
-      </c>
+      <c r="B17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>Navier serviceable rides/yr = corridor demand pool × capture rate (10% on contested corridors; ~90% on captive sole-operator transfer legs — see the per-row Capture % column)</t>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>OPEX lines (per boat, per year — no double-counting)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Vessels supported = FLOOR(Navier rides/yr ÷ pax/yr per boat);  Market rev = vessels × rev/boat. The 'Market sizing' tab rolls these up into the SOM → SAM → TAM ladder.</t>
+          <t>Energy — variable propulsion cost: kWh on revenue sailings × local $/kWh (Country opex tab). Excludes utility demand charges.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Crew — fully-loaded captain + relief: local captain wage × crew FTE factor (Country opex + Assumptions).</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>The scenario toggle (what we flex)</t>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Berth &amp; port admin — fixed annual berth, port fees, and local marine admin (Country opex tab). Excludes vessel H&amp;M+P&amp;I and fast-charge infrastructure.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>'Corridor economics' has a SCENARIO cell = THIN / MID / FULL. It flexes two levers: load factor (how full the boat is) and revenue-leg factor (how many legs earn full fare). MID is the headline. Change that one cell and the whole model recomputes. The right-hand Payback THIN/MID/FULL columns always show all three at once.</t>
+          <t>Maintenance — vessel annual maintenance reserve (Assumptions tab).</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Vessel insurance — commercial H&amp;M + P&amp;I as % of regional CAPEX (Assumptions % × Country opex CAPEX column).</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Fast-charge berth — dedicated fast-charge berth slot + utility demand charges (Assumptions default; overridable per market). Separate from per-kWh energy and berth/port admin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>From demand pool to fleet &amp; market size</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Navier serviceable rides/yr = corridor demand pool × capture rate (10% on contested corridors; ~90% on captive sole-operator transfer legs — see the per-row Capture % column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Vessels supported = FLOOR(Navier rides/yr ÷ pax/yr per boat);  Market rev = vessels × rev/boat. The 'Market sizing' tab rolls these up into the SOM → SAM → TAM ladder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>The scenario toggle (what we flex)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>'Corridor economics' has a SCENARIO cell = THIN / MID / FULL. It flexes load factor (occupancy) and revenue-leg factor (share of legs that earn full fare). Max trips/day is fixed across all three bands (see Assumptions). MID is the headline. Change SCENARIO and the whole model recomputes. Payback THIN/MID/FULL columns always show all three at once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Colour &amp; provenance legend</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="6" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">   Yellow = INPUTS you can change (fare, distance, demand, weather).</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="7" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">   Green  = COMPUTED by formula.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="2" t="inlineStr">
+    <row r="36">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   Every fare &amp; demand figure carries a Source tier (T1 official → T5 modeled) + Confidence (high/med/low). Null beats a wrong number: no published pool → blank, not a guess.</t>
         </is>
@@ -880,7 +939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1369,11 +1428,11 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>Insurance (% of capex/yr)</t>
+          <t>Mechanical uptime</t>
         </is>
       </c>
       <c r="B21" s="17" t="n">
-        <v>0.025</v>
+        <v>0.75</v>
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
@@ -1382,7 +1441,7 @@
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
@@ -1392,29 +1451,25 @@
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>H&amp;M + P&amp;I for a commercial passenger vessel ~2.5%/yr of capex; scales with regional capex overrides (Jaideep 2026-06-19).</t>
+          <t>Blade luxury aviation ~75-80% reliability uptime</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Charging &amp; berth (additional to marina+energy)</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="n">
-        <v>18000</v>
+          <t>Navier capture rate</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n">
+        <v>0.1</v>
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>USD/yr</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
+          <t>frac</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr"/>
       <c r="E22" s="13" t="inlineStr">
         <is>
           <t>med</t>
@@ -1422,29 +1477,25 @@
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>Dedicated fast-charge berth + demand charges, ADDITIONAL to marina overhead and energy (Jaideep 2026-06-19). L3-overridable.</t>
+          <t>Navier wins ~10% of a CONTESTED corridor demand pool (locked). Captive sole-operator transfer legs (captive:true / luxury_charter / hospitality archetypes) carry the captive rate instead — see per-row Capture %.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>Mechanical uptime</t>
+          <t>Captive capture rate (A′ corridors)</t>
         </is>
       </c>
       <c r="B23" s="17" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
           <t>frac</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
+      <c r="D23" s="13" t="inlineStr"/>
       <c r="E23" s="13" t="inlineStr">
         <is>
           <t>med</t>
@@ -1452,255 +1503,303 @@
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>Blade luxury aviation ~75-80% reliability uptime</t>
+          <t>Sole-operator water-access-only transfer legs (captive:true or luxury_charter/hospitality archetype): Navier IS the transfer fleet — capture ~90%. Applied per-row in the Capture % column.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>Navier capture rate</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="n">
-        <v>0.1</v>
+          <t>Discount factor (vs comparable fare)</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="n">
+        <v>1</v>
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
           <t>frac</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr"/>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>med</t>
+          <t>high</t>
         </is>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>Navier wins ~10% of a CONTESTED corridor demand pool (locked). Captive sole-operator transfer legs (captive:true / luxury_charter / hospitality archetypes) carry the captive rate instead — see per-row Capture %.</t>
+          <t>Market parity — better product, not cheaper (locked).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Captive capture rate (A′ corridors)</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="n">
-        <v>0.9</v>
+          <t>Diesel CO₂ per gallon</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="n">
+        <v>10.21</v>
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
+          <t>kg/gal</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t>US EPA: 10.21 kg CO2 per gallon marine/diesel</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>OPEX defaults  (global fallbacks — localized energy, crew, berth admin on Country opex tab)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>Conf.</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>Source / note</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>Vessel insurance — H&amp;M + P&amp;I (% of CAPEX/yr)</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
           <t>frac</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr"/>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>med</t>
         </is>
       </c>
-      <c r="F25" s="14" t="inlineStr">
-        <is>
-          <t>Sole-operator water-access-only transfer legs (captive:true or luxury_charter/hospitality archetype): Navier IS the transfer fleet — capture ~90%. Applied per-row in the Capture % column.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>Discount factor (vs comparable fare)</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
-        <is>
-          <t>frac</t>
-        </is>
-      </c>
-      <c r="D26" s="13" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="inlineStr">
-        <is>
-          <t>Market parity — better product, not cheaper (locked).</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>Diesel CO₂ per gallon</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="n">
-        <v>10.21</v>
-      </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>kg/gal</t>
-        </is>
-      </c>
-      <c r="D27" s="13" t="inlineStr">
-        <is>
-          <t>T1</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="inlineStr">
-        <is>
-          <t>US EPA: 10.21 kg CO2 per gallon marine/diesel</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>Utilization scenarios  (the two levers we flex)</t>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>Commercial vessel H&amp;M + P&amp;I ~2.5%/yr of regional CAPEX. Separate from berth/port admin in Country opex (Jaideep 2026-06-19).. Multiplied by regional CAPEX (Country opex col G). Not included in berth/port admin.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>Fast-charge berth &amp; demand charges (global default)</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>USD/yr</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>Dedicated fast-charge berth slot + utility demand charges. Excludes per-kWh propulsion energy and berth/port admin (Jaideep 2026-06-19). L3-overridable per market.. Dedicated charge berth + utility demand charges. Excludes per-kWh propulsion energy and berth/port admin. L3-overridable per market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>Utilization scenarios  (load factor + revenue-leg factor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>Scenario</t>
         </is>
       </c>
-      <c r="B30" s="10" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>Load factor</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
+      <c r="C33" s="10" t="inlineStr">
         <is>
           <t>Rev-leg factor</t>
         </is>
       </c>
-      <c r="D30" s="10" t="inlineStr"/>
-      <c r="E30" s="10" t="inlineStr"/>
-      <c r="F30" s="10" t="inlineStr">
+      <c r="D33" s="10" t="inlineStr"/>
+      <c r="E33" s="10" t="inlineStr"/>
+      <c r="F33" s="10" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="18" t="inlineStr">
         <is>
           <t>THIN</t>
         </is>
       </c>
-      <c r="B31" s="19" t="n">
+      <c r="B34" s="19" t="n">
         <v>0.45</v>
       </c>
-      <c r="C31" s="19" t="n">
+      <c r="C34" s="19" t="n">
         <v>0.55</v>
       </c>
-      <c r="F31" s="14" t="inlineStr">
+      <c r="F34" s="14" t="inlineStr">
         <is>
           <t>thin/one-way/seasonal corridor — conservative floor</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="18" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="18" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="B32" s="19" t="n">
+      <c r="B35" s="19" t="n">
         <v>0.55</v>
       </c>
-      <c r="C32" s="19" t="n">
+      <c r="C35" s="19" t="n">
         <v>0.65</v>
       </c>
-      <c r="F32" s="14" t="inlineStr">
+      <c r="F35" s="14" t="inlineStr">
         <is>
           <t>HEADLINE — realistic busy two-way corridor</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="18" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t>FULL</t>
         </is>
       </c>
-      <c r="B33" s="19" t="n">
+      <c r="B36" s="19" t="n">
         <v>0.7</v>
       </c>
-      <c r="C33" s="19" t="n">
+      <c r="C36" s="19" t="n">
         <v>0.75</v>
       </c>
-      <c r="F33" s="14" t="inlineStr">
+      <c r="F36" s="14" t="inlineStr">
         <is>
           <t>mature/dense corridor — optimistic ceiling</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="20" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>SCENARIO (toggle me)</t>
         </is>
       </c>
-      <c r="B35" s="21" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="C35" s="22" t="inlineStr">
+      <c r="C38" s="22" t="inlineStr">
         <is>
           <t>← set THIN / MID / FULL</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>Selected load factor</t>
         </is>
       </c>
-      <c r="B36" s="23">
-        <f>VLOOKUP(scenario,'Assumptions'!$A$31:$C$33,2,FALSE)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+      <c r="B39" s="23">
+        <f>VLOOKUP(scenario,'Assumptions'!$A$34:$C$36,2,FALSE)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>Selected rev-leg factor</t>
         </is>
       </c>
-      <c r="B37" s="23">
-        <f>VLOOKUP(scenario,'Assumptions'!$A$31:$C$33,3,FALSE)</f>
+      <c r="B40" s="23">
+        <f>VLOOKUP(scenario,'Assumptions'!$A$34:$C$36,3,FALSE)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A3:F3"/>
+  <mergeCells count="5">
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A3:F3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="B38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"THIN,MID,FULL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1730,7 +1829,7 @@
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>Country opex — L3 localized layer (VLOOKUP target for the engine)</t>
+          <t>Country opex — localized inputs (crew, energy, berth admin, CAPEX)</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1856,7 @@
       </c>
       <c r="E3" s="24" t="inlineStr">
         <is>
-          <t>Marina $/yr</t>
+          <t>Berth &amp; port admin $/yr</t>
         </is>
       </c>
       <c r="F3" s="24" t="inlineStr">
@@ -1772,7 +1871,7 @@
       </c>
       <c r="H3" s="24" t="inlineStr">
         <is>
-          <t>Source notes (captain | energy | marina)</t>
+          <t>Source notes (crew | energy | berth admin)</t>
         </is>
       </c>
     </row>
@@ -1845,10 +1944,10 @@
     <col width="11" customWidth="1" min="20" max="20"/>
     <col width="10" customWidth="1" min="21" max="21"/>
     <col width="10" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
     <col width="9" customWidth="1" min="24" max="24"/>
-    <col width="10" customWidth="1" min="25" max="25"/>
-    <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
     <col width="11" customWidth="1" min="27" max="27"/>
     <col width="10" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
@@ -2009,7 +2108,7 @@
       </c>
       <c r="W3" s="24" t="inlineStr">
         <is>
-          <t>Marina/yr</t>
+          <t>Berth &amp; port admin/yr</t>
         </is>
       </c>
       <c r="X3" s="24" t="inlineStr">
@@ -2019,12 +2118,12 @@
       </c>
       <c r="Y3" s="24" t="inlineStr">
         <is>
-          <t>Insurance/yr</t>
+          <t>Vessel insurance/yr</t>
         </is>
       </c>
       <c r="Z3" s="24" t="inlineStr">
         <is>
-          <t>Charge+berth/yr</t>
+          <t>Fast-charge berth/yr</t>
         </is>
       </c>
       <c r="AA3" s="24" t="inlineStr">

--- a/finance/_refresh_qatar.xlsx
+++ b/finance/_refresh_qatar.xlsx
@@ -45,8 +45,8 @@
     <definedName name="load_sel">'Assumptions'!$B$39</definedName>
     <definedName name="revleg_sel">'Assumptions'!$B$40</definedName>
     <definedName name="country_opex">'Country opex'!$A$4:$G$4</definedName>
-    <definedName name="som_floor_fleet">'Corridor economics'!$D$18</definedName>
-    <definedName name="som_floor_rev">'Corridor economics'!$E$18</definedName>
+    <definedName name="som_floor_fleet">'Corridor economics'!$D$21</definedName>
+    <definedName name="som_floor_rev">'Corridor economics'!$E$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1919,7 +1919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX21"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1964,14 +1964,15 @@
     <col width="9" customWidth="1" min="40" max="40"/>
     <col width="13" customWidth="1" min="41" max="41"/>
     <col width="26" customWidth="1" min="42" max="42"/>
-    <col width="16" customWidth="1" min="43" max="43"/>
+    <col width="14" customWidth="1" min="43" max="43"/>
     <col width="16" customWidth="1" min="44" max="44"/>
-    <col width="9" customWidth="1" min="45" max="45"/>
+    <col width="16" customWidth="1" min="45" max="45"/>
     <col width="9" customWidth="1" min="46" max="46"/>
     <col width="9" customWidth="1" min="47" max="47"/>
     <col width="9" customWidth="1" min="48" max="48"/>
-    <col width="50" customWidth="1" min="49" max="49"/>
+    <col width="9" customWidth="1" min="49" max="49"/>
     <col width="50" customWidth="1" min="50" max="50"/>
+    <col width="50" customWidth="1" min="51" max="51"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2208,40 +2209,45 @@
       </c>
       <c r="AQ3" s="24" t="inlineStr">
         <is>
+          <t>Floor bucket (aggregate status)</t>
+        </is>
+      </c>
+      <c r="AR3" s="24" t="inlineStr">
+        <is>
           <t>Forward SAM (2030-dated; held OUT of grounded floor)</t>
         </is>
       </c>
-      <c r="AR3" s="24" t="inlineStr">
+      <c r="AS3" s="24" t="inlineStr">
         <is>
           <t>Upside tier (LB-99; held OUT of grounded floor)</t>
         </is>
       </c>
-      <c r="AS3" s="24" t="inlineStr">
+      <c r="AT3" s="24" t="inlineStr">
         <is>
           <t>Fleet ceiling (captive villas/25)</t>
         </is>
       </c>
-      <c r="AT3" s="24" t="inlineStr">
+      <c r="AU3" s="24" t="inlineStr">
         <is>
           <t>Payback THIN</t>
         </is>
       </c>
-      <c r="AU3" s="24" t="inlineStr">
+      <c r="AV3" s="24" t="inlineStr">
         <is>
           <t>Payback MID</t>
         </is>
       </c>
-      <c r="AV3" s="24" t="inlineStr">
+      <c r="AW3" s="24" t="inlineStr">
         <is>
           <t>Payback FULL</t>
         </is>
       </c>
-      <c r="AW3" s="24" t="inlineStr">
+      <c r="AX3" s="24" t="inlineStr">
         <is>
           <t>Fare source (provenance)</t>
         </is>
       </c>
-      <c r="AX3" s="24" t="inlineStr">
+      <c r="AY3" s="24" t="inlineStr">
         <is>
           <t>Demand source (provenance)</t>
         </is>
@@ -2379,7 +2385,7 @@
         <v/>
       </c>
       <c r="AL4" s="34">
-        <f>IF(OR(AG4="",R4=0),"",MIN(IF(AS4="",9.9E+99,AS4),FLOOR(AK4/R4,1)))</f>
+        <f>IF(OR(AG4="",R4=0),"",MIN(IF(AT4="",9.9E+99,AT4),FLOOR(AK4/R4,1)))</f>
         <v/>
       </c>
       <c r="AM4" s="38">
@@ -2387,7 +2393,7 @@
         <v/>
       </c>
       <c r="AN4" s="36">
-        <f>IF(OR(AG4="",R4=0),"",MIN(IF(AS4="",9.9E+99,AS4),AK4/R4))</f>
+        <f>IF(OR(AG4="",R4=0),"",MIN(IF(AT4="",9.9E+99,AT4),AK4/R4))</f>
         <v/>
       </c>
       <c r="AO4" s="38">
@@ -2395,23 +2401,28 @@
         <v/>
       </c>
       <c r="AP4" s="40" t="n"/>
-      <c r="AQ4" s="41" t="n"/>
+      <c r="AQ4" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
       <c r="AR4" s="41" t="n"/>
-      <c r="AS4" s="42" t="n"/>
-      <c r="AT4" s="43">
+      <c r="AS4" s="41" t="n"/>
+      <c r="AT4" s="42" t="n"/>
+      <c r="AU4" s="43">
         <f>IF(((S4*pax_cap*load_thin*ROUND(K4*L4*revleg_thin,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_thin,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4))&lt;=0,"",VLOOKUP(B4,country_opex,7,FALSE)/((S4*pax_cap*load_thin*ROUND(K4*L4*revleg_thin,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_thin,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4)))</f>
         <v/>
       </c>
-      <c r="AU4" s="43">
+      <c r="AV4" s="43">
         <f>IF(((S4*pax_cap*load_mid*ROUND(K4*L4*revleg_mid,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_mid,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4))&lt;=0,"",VLOOKUP(B4,country_opex,7,FALSE)/((S4*pax_cap*load_mid*ROUND(K4*L4*revleg_mid,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_mid,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4)))</f>
         <v/>
       </c>
-      <c r="AV4" s="43">
+      <c r="AW4" s="43">
         <f>IF(((S4*pax_cap*load_full*ROUND(K4*L4*revleg_full,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_full,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4))&lt;=0,"",VLOOKUP(B4,country_opex,7,FALSE)/((S4*pax_cap*load_full*ROUND(K4*L4*revleg_full,0))-(((battery/range_nm)*D4*ROUND(K4*L4*revleg_full,0)*VLOOKUP(B4,country_opex,3,FALSE))+V4+W4+X4+Y4+Z4)))</f>
         <v/>
       </c>
-      <c r="AW4" s="44" t="n"/>
       <c r="AX4" s="44" t="n"/>
+      <c r="AY4" s="44" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="29" t="inlineStr">
@@ -2545,7 +2556,7 @@
         <v/>
       </c>
       <c r="AL5" s="34">
-        <f>IF(OR(AG5="",R5=0),"",MIN(IF(AS5="",9.9E+99,AS5),FLOOR(AK5/R5,1)))</f>
+        <f>IF(OR(AG5="",R5=0),"",MIN(IF(AT5="",9.9E+99,AT5),FLOOR(AK5/R5,1)))</f>
         <v/>
       </c>
       <c r="AM5" s="38">
@@ -2553,7 +2564,7 @@
         <v/>
       </c>
       <c r="AN5" s="36">
-        <f>IF(OR(AG5="",R5=0),"",MIN(IF(AS5="",9.9E+99,AS5),AK5/R5))</f>
+        <f>IF(OR(AG5="",R5=0),"",MIN(IF(AT5="",9.9E+99,AT5),AK5/R5))</f>
         <v/>
       </c>
       <c r="AO5" s="38">
@@ -2561,23 +2572,28 @@
         <v/>
       </c>
       <c r="AP5" s="40" t="n"/>
-      <c r="AQ5" s="41" t="n"/>
+      <c r="AQ5" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
       <c r="AR5" s="41" t="n"/>
-      <c r="AS5" s="42" t="n"/>
-      <c r="AT5" s="43">
+      <c r="AS5" s="41" t="n"/>
+      <c r="AT5" s="42" t="n"/>
+      <c r="AU5" s="43">
         <f>IF(((S5*pax_cap*load_thin*ROUND(K5*L5*revleg_thin,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_thin,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5))&lt;=0,"",VLOOKUP(B5,country_opex,7,FALSE)/((S5*pax_cap*load_thin*ROUND(K5*L5*revleg_thin,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_thin,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5)))</f>
         <v/>
       </c>
-      <c r="AU5" s="43">
+      <c r="AV5" s="43">
         <f>IF(((S5*pax_cap*load_mid*ROUND(K5*L5*revleg_mid,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_mid,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5))&lt;=0,"",VLOOKUP(B5,country_opex,7,FALSE)/((S5*pax_cap*load_mid*ROUND(K5*L5*revleg_mid,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_mid,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5)))</f>
         <v/>
       </c>
-      <c r="AV5" s="43">
+      <c r="AW5" s="43">
         <f>IF(((S5*pax_cap*load_full*ROUND(K5*L5*revleg_full,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_full,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5))&lt;=0,"",VLOOKUP(B5,country_opex,7,FALSE)/((S5*pax_cap*load_full*ROUND(K5*L5*revleg_full,0))-(((battery/range_nm)*D5*ROUND(K5*L5*revleg_full,0)*VLOOKUP(B5,country_opex,3,FALSE))+V5+W5+X5+Y5+Z5)))</f>
         <v/>
       </c>
-      <c r="AW5" s="44" t="n"/>
       <c r="AX5" s="44" t="n"/>
+      <c r="AY5" s="44" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="29" t="inlineStr">
@@ -2598,19 +2614,9 @@
       <c r="D6" s="31" t="n">
         <v>4.4</v>
       </c>
-      <c r="E6" s="26" t="n">
-        <v>10.99</v>
-      </c>
-      <c r="F6" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="G6" s="32" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
+      <c r="E6" s="26" t="n"/>
+      <c r="F6" s="32" t="n"/>
+      <c r="G6" s="32" t="n"/>
       <c r="H6" s="19" t="n">
         <v>1</v>
       </c>
@@ -2623,7 +2629,7 @@
         <v/>
       </c>
       <c r="K6" s="34">
-        <f>MIN(27,FLOOR(60*service_hr/J6,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J6,1))</f>
         <v/>
       </c>
       <c r="L6" s="34">
@@ -2710,19 +2716,9 @@
         <f>((D6*O6/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D6*O6*VLOOKUP(B6,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG6" s="31" t="n">
-        <v>50000</v>
-      </c>
-      <c r="AH6" s="32" t="inlineStr">
-        <is>
-          <t>T5</t>
-        </is>
-      </c>
-      <c r="AI6" s="32" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
+      <c r="AG6" s="31" t="n"/>
+      <c r="AH6" s="32" t="n"/>
+      <c r="AI6" s="32" t="n"/>
       <c r="AJ6" s="39" t="n">
         <v>0.1</v>
       </c>
@@ -2731,7 +2727,7 @@
         <v/>
       </c>
       <c r="AL6" s="34">
-        <f>IF(OR(AG6="",R6=0),"",MIN(IF(AS6="",9.9E+99,AS6),FLOOR(AK6/R6,1)))</f>
+        <f>IF(OR(AG6="",R6=0),"",MIN(IF(AT6="",9.9E+99,AT6),FLOOR(AK6/R6,1)))</f>
         <v/>
       </c>
       <c r="AM6" s="38">
@@ -2739,7 +2735,7 @@
         <v/>
       </c>
       <c r="AN6" s="36">
-        <f>IF(OR(AG6="",R6=0),"",MIN(IF(AS6="",9.9E+99,AS6),AK6/R6))</f>
+        <f>IF(OR(AG6="",R6=0),"",MIN(IF(AT6="",9.9E+99,AT6),AK6/R6))</f>
         <v/>
       </c>
       <c r="AO6" s="38">
@@ -2747,31 +2743,28 @@
         <v/>
       </c>
       <c r="AP6" s="40" t="n"/>
-      <c r="AQ6" s="41" t="n"/>
+      <c r="AQ6" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
       <c r="AR6" s="41" t="n"/>
-      <c r="AS6" s="42" t="n"/>
-      <c r="AT6" s="43">
+      <c r="AS6" s="41" t="n"/>
+      <c r="AT6" s="42" t="n"/>
+      <c r="AU6" s="43">
         <f>IF(((S6*pax_cap*load_thin*ROUND(K6*L6*revleg_thin,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_thin,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6))&lt;=0,"",VLOOKUP(B6,country_opex,7,FALSE)/((S6*pax_cap*load_thin*ROUND(K6*L6*revleg_thin,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_thin,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6)))</f>
         <v/>
       </c>
-      <c r="AU6" s="43">
+      <c r="AV6" s="43">
         <f>IF(((S6*pax_cap*load_mid*ROUND(K6*L6*revleg_mid,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_mid,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6))&lt;=0,"",VLOOKUP(B6,country_opex,7,FALSE)/((S6*pax_cap*load_mid*ROUND(K6*L6*revleg_mid,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_mid,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6)))</f>
         <v/>
       </c>
-      <c r="AV6" s="43">
+      <c r="AW6" s="43">
         <f>IF(((S6*pax_cap*load_full*ROUND(K6*L6*revleg_full,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_full,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6))&lt;=0,"",VLOOKUP(B6,country_opex,7,FALSE)/((S6*pax_cap*load_full*ROUND(K6*L6*revleg_full,0))-(((battery/range_nm)*D6*ROUND(K6*L6*revleg_full,0)*VLOOKUP(B6,country_opex,3,FALSE))+V6+W6+X6+Y6+Z6)))</f>
         <v/>
       </c>
-      <c r="AW6" s="44" t="inlineStr">
-        <is>
-          <t>Ronautica (UDC official Pearl marine operator) gate-to-gate water shuttle QAR 40/pp (USD 10.99) — premium per-seat tier on-corridor. Cheap tier: Mina Link scheduled shuttle QAR 25/pp (USD 6.87, launched Jul 2025; geography conflict between sources — timeoutdoha says Old Doha Port&lt;-&gt;Pearl, launch coverage says intra-port loop — so held to ladder, not anchor). Intra-Pearl premium: Porto Arabia&lt;-&gt;Qanat Quartier QAR 80/pp ($21.98).</t>
-        </is>
-      </c>
-      <c r="AX6" s="44" t="inlineStr">
-        <is>
-          <t>On-corridor T1 anchors: Old Doha Port 7M+ visitors 2025 with 97% leasing occupancy, and 87 cruise ships / 396,000+ cruise passengers in the 2024-25 season (QNA/Old Doha Port CEO, 31-Dec-2025 — T1). Pearl Island ~52,000 residents, ~20M vehicle entries/yr (UDC). MOT Pearl Ferry Stop infrastructure complete (mot.gov.qa). Mina Link shuttle (QAR 25/pp, Brooq Tourism, daily 10:00-21:30): ridership unpublished; GEOGRAPHY FLAG — most launch coverage describes it as Containers Yard &lt;-&gt; Mina District (an INTRA-PORT scenic loop), not Old Doha Port &lt;-&gt; The Pearl, so it is a weak on-corridor proxy.</t>
-        </is>
-      </c>
+      <c r="AX6" s="44" t="n"/>
+      <c r="AY6" s="44" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="29" t="inlineStr">
@@ -2786,15 +2779,25 @@
       </c>
       <c r="C7" s="30" t="inlineStr">
         <is>
-          <t>Doha → Banana Island</t>
+          <t>The Pearl-Qatar (Marsa Arabia) → Doha Corniche / Old Doha Port</t>
         </is>
       </c>
       <c r="D7" s="31" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E7" s="26" t="n"/>
-      <c r="F7" s="32" t="n"/>
-      <c r="G7" s="32" t="n"/>
+        <v>4.4</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="F7" s="32" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="G7" s="32" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
       <c r="H7" s="19" t="n">
         <v>1</v>
       </c>
@@ -2894,9 +2897,19 @@
         <f>((D7*O7/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D7*O7*VLOOKUP(B7,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG7" s="31" t="n"/>
-      <c r="AH7" s="32" t="n"/>
-      <c r="AI7" s="32" t="n"/>
+      <c r="AG7" s="31" t="n">
+        <v>50000</v>
+      </c>
+      <c r="AH7" s="32" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="AI7" s="32" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
       <c r="AJ7" s="39" t="n">
         <v>0.1</v>
       </c>
@@ -2905,7 +2918,7 @@
         <v/>
       </c>
       <c r="AL7" s="34">
-        <f>IF(OR(AG7="",R7=0),"",MIN(IF(AS7="",9.9E+99,AS7),FLOOR(AK7/R7,1)))</f>
+        <f>IF(OR(AG7="",R7=0),"",MIN(IF(AT7="",9.9E+99,AT7),FLOOR(AK7/R7,1)))</f>
         <v/>
       </c>
       <c r="AM7" s="38">
@@ -2913,7 +2926,7 @@
         <v/>
       </c>
       <c r="AN7" s="36">
-        <f>IF(OR(AG7="",R7=0),"",MIN(IF(AS7="",9.9E+99,AS7),AK7/R7))</f>
+        <f>IF(OR(AG7="",R7=0),"",MIN(IF(AT7="",9.9E+99,AT7),AK7/R7))</f>
         <v/>
       </c>
       <c r="AO7" s="38">
@@ -2921,23 +2934,36 @@
         <v/>
       </c>
       <c r="AP7" s="40" t="n"/>
-      <c r="AQ7" s="41" t="n"/>
+      <c r="AQ7" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
       <c r="AR7" s="41" t="n"/>
-      <c r="AS7" s="42" t="n"/>
-      <c r="AT7" s="43">
+      <c r="AS7" s="41" t="n"/>
+      <c r="AT7" s="42" t="n"/>
+      <c r="AU7" s="43">
         <f>IF(((S7*pax_cap*load_thin*ROUND(K7*L7*revleg_thin,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_thin,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7))&lt;=0,"",VLOOKUP(B7,country_opex,7,FALSE)/((S7*pax_cap*load_thin*ROUND(K7*L7*revleg_thin,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_thin,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7)))</f>
         <v/>
       </c>
-      <c r="AU7" s="43">
+      <c r="AV7" s="43">
         <f>IF(((S7*pax_cap*load_mid*ROUND(K7*L7*revleg_mid,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_mid,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7))&lt;=0,"",VLOOKUP(B7,country_opex,7,FALSE)/((S7*pax_cap*load_mid*ROUND(K7*L7*revleg_mid,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_mid,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7)))</f>
         <v/>
       </c>
-      <c r="AV7" s="43">
+      <c r="AW7" s="43">
         <f>IF(((S7*pax_cap*load_full*ROUND(K7*L7*revleg_full,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_full,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7))&lt;=0,"",VLOOKUP(B7,country_opex,7,FALSE)/((S7*pax_cap*load_full*ROUND(K7*L7*revleg_full,0))-(((battery/range_nm)*D7*ROUND(K7*L7*revleg_full,0)*VLOOKUP(B7,country_opex,3,FALSE))+V7+W7+X7+Y7+Z7)))</f>
         <v/>
       </c>
-      <c r="AW7" s="44" t="n"/>
-      <c r="AX7" s="44" t="n"/>
+      <c r="AX7" s="44" t="inlineStr">
+        <is>
+          <t>Ronautica (UDC official Pearl marine operator) gate-to-gate water shuttle QAR 40/pp (USD 10.99) — premium per-seat tier on-corridor. Cheap tier: Mina Link scheduled shuttle QAR 25/pp (USD 6.87, launched Jul 2025; geography conflict between sources — timeoutdoha says Old Doha Port&lt;-&gt;Pearl, launch coverage says intra-port loop — so held to ladder, not anchor). Intra-Pearl premium: Porto Arabia&lt;-&gt;Qanat Quartier QAR 80/pp ($21.98).</t>
+        </is>
+      </c>
+      <c r="AY7" s="44" t="inlineStr">
+        <is>
+          <t>On-corridor T1 anchors: Old Doha Port 7M+ visitors 2025 with 97% leasing occupancy, and 87 cruise ships / 396,000+ cruise passengers in the 2024-25 season (QNA/Old Doha Port CEO, 31-Dec-2025 — T1). Pearl Island ~52,000 residents, ~20M vehicle entries/yr (UDC). MOT Pearl Ferry Stop infrastructure complete (mot.gov.qa). Mina Link shuttle (QAR 25/pp, Brooq Tourism, daily 10:00-21:30): ridership unpublished; GEOGRAPHY FLAG — most launch coverage describes it as Containers Yard &lt;-&gt; Mina District (an INTRA-PORT scenic loop), not Old Doha Port &lt;-&gt; The Pearl, so it is a weak on-corridor proxy.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="29" t="inlineStr">
@@ -2952,25 +2978,15 @@
       </c>
       <c r="C8" s="30" t="inlineStr">
         <is>
-          <t>Doha (Al Shyoukh Terminal) → Banana Island Resort (Anantara)</t>
+          <t>Doha → Banana Island</t>
         </is>
       </c>
       <c r="D8" s="31" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="E8" s="26" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="F8" s="32" t="inlineStr">
-        <is>
-          <t>T3</t>
-        </is>
-      </c>
-      <c r="G8" s="32" t="inlineStr">
-        <is>
-          <t>med</t>
-        </is>
-      </c>
+        <v>4.5</v>
+      </c>
+      <c r="E8" s="26" t="n"/>
+      <c r="F8" s="32" t="n"/>
+      <c r="G8" s="32" t="n"/>
       <c r="H8" s="19" t="n">
         <v>1</v>
       </c>
@@ -2983,7 +2999,7 @@
         <v/>
       </c>
       <c r="K8" s="34">
-        <f>MIN(15,FLOOR(60*service_hr/J8,1))</f>
+        <f>MIN(27,FLOOR(60*service_hr/J8,1))</f>
         <v/>
       </c>
       <c r="L8" s="34">
@@ -3070,28 +3086,18 @@
         <f>((D8*O8/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D8*O8*VLOOKUP(B8,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG8" s="31" t="n">
-        <v>85000</v>
-      </c>
-      <c r="AH8" s="32" t="inlineStr">
-        <is>
-          <t>T4</t>
-        </is>
-      </c>
-      <c r="AI8" s="32" t="inlineStr">
-        <is>
-          <t>med-low</t>
-        </is>
-      </c>
+      <c r="AG8" s="31" t="n"/>
+      <c r="AH8" s="32" t="n"/>
+      <c r="AI8" s="32" t="n"/>
       <c r="AJ8" s="39" t="n">
-        <v>0.9</v>
+        <v>0.1</v>
       </c>
       <c r="AK8" s="34">
         <f>IF(AG8="","",AG8*AJ8)</f>
         <v/>
       </c>
       <c r="AL8" s="34">
-        <f>IF(OR(AG8="",R8=0),"",MIN(IF(AS8="",9.9E+99,AS8),FLOOR(AK8/R8,1)))</f>
+        <f>IF(OR(AG8="",R8=0),"",MIN(IF(AT8="",9.9E+99,AT8),FLOOR(AK8/R8,1)))</f>
         <v/>
       </c>
       <c r="AM8" s="38">
@@ -3099,7 +3105,7 @@
         <v/>
       </c>
       <c r="AN8" s="36">
-        <f>IF(OR(AG8="",R8=0),"",MIN(IF(AS8="",9.9E+99,AS8),AK8/R8))</f>
+        <f>IF(OR(AG8="",R8=0),"",MIN(IF(AT8="",9.9E+99,AT8),AK8/R8))</f>
         <v/>
       </c>
       <c r="AO8" s="38">
@@ -3107,31 +3113,28 @@
         <v/>
       </c>
       <c r="AP8" s="40" t="n"/>
-      <c r="AQ8" s="41" t="n"/>
+      <c r="AQ8" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
       <c r="AR8" s="41" t="n"/>
-      <c r="AS8" s="42" t="n"/>
-      <c r="AT8" s="43">
+      <c r="AS8" s="41" t="n"/>
+      <c r="AT8" s="42" t="n"/>
+      <c r="AU8" s="43">
         <f>IF(((S8*pax_cap*load_thin*ROUND(K8*L8*revleg_thin,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_thin,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8))&lt;=0,"",VLOOKUP(B8,country_opex,7,FALSE)/((S8*pax_cap*load_thin*ROUND(K8*L8*revleg_thin,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_thin,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8)))</f>
         <v/>
       </c>
-      <c r="AU8" s="43">
+      <c r="AV8" s="43">
         <f>IF(((S8*pax_cap*load_mid*ROUND(K8*L8*revleg_mid,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_mid,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8))&lt;=0,"",VLOOKUP(B8,country_opex,7,FALSE)/((S8*pax_cap*load_mid*ROUND(K8*L8*revleg_mid,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_mid,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8)))</f>
         <v/>
       </c>
-      <c r="AV8" s="43">
+      <c r="AW8" s="43">
         <f>IF(((S8*pax_cap*load_full*ROUND(K8*L8*revleg_full,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_full,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8))&lt;=0,"",VLOOKUP(B8,country_opex,7,FALSE)/((S8*pax_cap*load_full*ROUND(K8*L8*revleg_full,0))-(((battery/range_nm)*D8*ROUND(K8*L8*revleg_full,0)*VLOOKUP(B8,country_opex,3,FALSE))+V8+W8+X8+Y8+Z8)))</f>
         <v/>
       </c>
-      <c r="AW8" s="44" t="inlineStr">
-        <is>
-          <t>Anantara official: day pass QAR 395/adult ($108.51) incl RT luxury catamaran transfer + QAR 345 credits. De-bundled transfer component: child rate QAR 200 RT no credits =&gt; ~QAR 100/way ~ USD 27.5/pp one-way pure-transfer value (honest band $14-55 RT).</t>
-        </is>
-      </c>
-      <c r="AX8" s="44" t="inlineStr">
-        <is>
-          <t>Anantara Banana Island official: 141 keys (anantara.com/visitqatar, T1); access is BOAT-ONLY via ~45-51-pax luxury catamaran from Al Shyoukh Terminal, 25-30 min, scheduled ~hourly 09:00-21:00 (booking.com listing; adventureparkdoha.com '45-passenger catamaran operates regularly'; observed 51-pax config). Qatar national hotel occupancy 71% 2025 (Qatar Tourism/ValuStrat, T2). Day-pass product QAR 395/adult incl. RT transfer (anantara.com, T1) adds day-tripper volume.</t>
-        </is>
-      </c>
+      <c r="AX8" s="44" t="n"/>
+      <c r="AY8" s="44" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="29" t="inlineStr">
@@ -3146,25 +3149,15 @@
       </c>
       <c r="C9" s="30" t="inlineStr">
         <is>
-          <t>West Bay / Corniche (Doha) → Lusail Marina &amp; Place Vendôme</t>
+          <t>Doha (Al Shyoukh Terminal) → Banana Island Resort (Anantara)</t>
         </is>
       </c>
       <c r="D9" s="31" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="E9" s="26" t="n">
-        <v>16</v>
-      </c>
-      <c r="F9" s="32" t="inlineStr">
-        <is>
-          <t>T5</t>
-        </is>
-      </c>
-      <c r="G9" s="32" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
+        <v>4.9</v>
+      </c>
+      <c r="E9" s="26" t="n"/>
+      <c r="F9" s="32" t="n"/>
+      <c r="G9" s="32" t="n"/>
       <c r="H9" s="19" t="n">
         <v>1</v>
       </c>
@@ -3177,7 +3170,7 @@
         <v/>
       </c>
       <c r="K9" s="34">
-        <f>MIN(27,FLOOR(60*service_hr/J9,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J9,1))</f>
         <v/>
       </c>
       <c r="L9" s="34">
@@ -3264,19 +3257,9 @@
         <f>((D9*O9/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D9*O9*VLOOKUP(B9,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG9" s="31" t="n">
-        <v>75000</v>
-      </c>
-      <c r="AH9" s="32" t="inlineStr">
-        <is>
-          <t>T5</t>
-        </is>
-      </c>
-      <c r="AI9" s="32" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
+      <c r="AG9" s="31" t="n"/>
+      <c r="AH9" s="32" t="n"/>
+      <c r="AI9" s="32" t="n"/>
       <c r="AJ9" s="39" t="n">
         <v>0.1</v>
       </c>
@@ -3285,7 +3268,7 @@
         <v/>
       </c>
       <c r="AL9" s="34">
-        <f>IF(OR(AG9="",R9=0),"",MIN(IF(AS9="",9.9E+99,AS9),FLOOR(AK9/R9,1)))</f>
+        <f>IF(OR(AG9="",R9=0),"",MIN(IF(AT9="",9.9E+99,AT9),FLOOR(AK9/R9,1)))</f>
         <v/>
       </c>
       <c r="AM9" s="38">
@@ -3293,7 +3276,7 @@
         <v/>
       </c>
       <c r="AN9" s="36">
-        <f>IF(OR(AG9="",R9=0),"",MIN(IF(AS9="",9.9E+99,AS9),AK9/R9))</f>
+        <f>IF(OR(AG9="",R9=0),"",MIN(IF(AT9="",9.9E+99,AT9),AK9/R9))</f>
         <v/>
       </c>
       <c r="AO9" s="38">
@@ -3301,35 +3284,28 @@
         <v/>
       </c>
       <c r="AP9" s="40" t="n"/>
-      <c r="AQ9" s="41" t="inlineStr">
-        <is>
-          <t>FWD-SAM (2030)</t>
+      <c r="AQ9" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
         </is>
       </c>
       <c r="AR9" s="41" t="n"/>
-      <c r="AS9" s="42" t="n"/>
-      <c r="AT9" s="43">
+      <c r="AS9" s="41" t="n"/>
+      <c r="AT9" s="42" t="n"/>
+      <c r="AU9" s="43">
         <f>IF(((S9*pax_cap*load_thin*ROUND(K9*L9*revleg_thin,0))-(((battery/range_nm)*D9*ROUND(K9*L9*revleg_thin,0)*VLOOKUP(B9,country_opex,3,FALSE))+V9+W9+X9+Y9+Z9))&lt;=0,"",VLOOKUP(B9,country_opex,7,FALSE)/((S9*pax_cap*load_thin*ROUND(K9*L9*revleg_thin,0))-(((battery/range_nm)*D9*ROUND(K9*L9*revleg_thin,0)*VLOOKUP(B9,country_opex,3,FALSE))+V9+W9+X9+Y9+Z9)))</f>
         <v/>
       </c>
-      <c r="AU9" s="43">
+      <c r="AV9" s="43">
         <f>IF(((S9*pax_cap*load_mid*ROUND(K9*L9*revleg_mid,0))-(((battery/range_nm)*D9*ROUND(K9*L9*revleg_mid,0)*VLOOKUP(B9,country_opex,3,FALSE))+V9+W9+X9+Y9+Z9))&lt;=0,"",VLOOKUP(B9,country_opex,7,FALSE)/((S9*pax_cap*load_mid*ROUND(K9*L9*revleg_mid,0))-(((battery/range_nm)*D9*ROUND(K9*L9*revleg_mid,0)*VLOOKUP(B9,country_opex,3,FALSE))+V9+W9+X9+Y9+Z9)))</f>
         <v/>
       </c>
-      <c r="AV9" s="43">
+      <c r="AW9" s="43">
         <f>IF(((S9*pax_cap*load_full*ROUND(K9*L9*revleg_full,0))-(((battery/range_nm)*D9*ROUND(K9*L9*revleg_full,0)*VLOOKUP(B9,country_opex,3,FALSE))+V9+W9+X9+Y9+Z9))&lt;=0,"",VLOOKUP(B9,country_opex,7,FALSE)/((S9*pax_cap*load_full*ROUND(K9*L9*revleg_full,0))-(((battery/range_nm)*D9*ROUND(K9*L9*revleg_full,0)*VLOOKUP(B9,country_opex,3,FALSE))+V9+W9+X9+Y9+Z9)))</f>
         <v/>
       </c>
-      <c r="AW9" s="44" t="inlineStr">
-        <is>
-          <t>No scheduled service yet: MOT Water Taxi Phase-1 INFRASTRUCTURE complete 7 Nov 2024 (Lusail Ferry Terminal + Pearl &amp; Corniche stops, EV-charger-fitted) but operator unselected, no fare published (mot.gov.qa). Cascaded from on-network premium per-seat anchor Ronautica Pearl gate-to-gate QAR 40/pp (USD 10.99) scaled per-nm 4.4-&gt;6.3nm =&gt; ~$15.7. Leisure upper bound: Blue Pearl shared speedboat West Bay QAR 160/pp ($43.95).</t>
-        </is>
-      </c>
-      <c r="AX9" s="44" t="inlineStr">
-        <is>
-          <t>No marine service operates on this corridor today (greenfield; MOT Water Taxi Phase-1 INFRASTRUCTURE complete Nov-2024 — Lusail Ferry Terminal + Corniche Ferry Stop sit EXACTLY on this corridor's endpoints, with electric-ferry chargers — but operator not yet selected; network capacity unpublished, mot.gov.qa). Destination pools (all LAND-arriving, R3-LAND caveat): Al Maha Island Lusail target 1.5M visitors/yr (Gulf Times/developer); Place Vendome mall claims 16.5M annual footfall (UDC leasing brochure 2025, marketing-grade); Lusail Boulevard 250k visitors on NYE 2025 alone (wgoqatar); Doha Corniche promenade has NO published count. Qatar 5.08M intl visitors 2024 / 5.1M 2025 (Qatar Tourism, T1).</t>
-        </is>
-      </c>
+      <c r="AX9" s="44" t="n"/>
+      <c r="AY9" s="44" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="29" t="inlineStr">
@@ -3344,15 +3320,25 @@
       </c>
       <c r="C10" s="30" t="inlineStr">
         <is>
-          <t>Doha → Lusail Marina</t>
+          <t>Doha (Al Shyoukh Terminal) → Banana Island Resort (Anantara)</t>
         </is>
       </c>
       <c r="D10" s="31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E10" s="26" t="n"/>
-      <c r="F10" s="32" t="n"/>
-      <c r="G10" s="32" t="n"/>
+        <v>4.9</v>
+      </c>
+      <c r="E10" s="26" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="F10" s="32" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="G10" s="32" t="inlineStr">
+        <is>
+          <t>med</t>
+        </is>
+      </c>
       <c r="H10" s="19" t="n">
         <v>1</v>
       </c>
@@ -3365,7 +3351,7 @@
         <v/>
       </c>
       <c r="K10" s="34">
-        <f>MIN(27,FLOOR(60*service_hr/J10,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J10,1))</f>
         <v/>
       </c>
       <c r="L10" s="34">
@@ -3452,18 +3438,28 @@
         <f>((D10*O10/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D10*O10*VLOOKUP(B10,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG10" s="31" t="n"/>
-      <c r="AH10" s="32" t="n"/>
-      <c r="AI10" s="32" t="n"/>
+      <c r="AG10" s="31" t="n">
+        <v>85000</v>
+      </c>
+      <c r="AH10" s="32" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="AI10" s="32" t="inlineStr">
+        <is>
+          <t>med-low</t>
+        </is>
+      </c>
       <c r="AJ10" s="39" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="AK10" s="34">
         <f>IF(AG10="","",AG10*AJ10)</f>
         <v/>
       </c>
       <c r="AL10" s="34">
-        <f>IF(OR(AG10="",R10=0),"",MIN(IF(AS10="",9.9E+99,AS10),FLOOR(AK10/R10,1)))</f>
+        <f>IF(OR(AG10="",R10=0),"",MIN(IF(AT10="",9.9E+99,AT10),FLOOR(AK10/R10,1)))</f>
         <v/>
       </c>
       <c r="AM10" s="38">
@@ -3471,7 +3467,7 @@
         <v/>
       </c>
       <c r="AN10" s="36">
-        <f>IF(OR(AG10="",R10=0),"",MIN(IF(AS10="",9.9E+99,AS10),AK10/R10))</f>
+        <f>IF(OR(AG10="",R10=0),"",MIN(IF(AT10="",9.9E+99,AT10),AK10/R10))</f>
         <v/>
       </c>
       <c r="AO10" s="38">
@@ -3479,23 +3475,36 @@
         <v/>
       </c>
       <c r="AP10" s="40" t="n"/>
-      <c r="AQ10" s="41" t="n"/>
+      <c r="AQ10" s="32" t="inlineStr">
+        <is>
+          <t>Grounded</t>
+        </is>
+      </c>
       <c r="AR10" s="41" t="n"/>
-      <c r="AS10" s="42" t="n"/>
-      <c r="AT10" s="43">
+      <c r="AS10" s="41" t="n"/>
+      <c r="AT10" s="42" t="n"/>
+      <c r="AU10" s="43">
         <f>IF(((S10*pax_cap*load_thin*ROUND(K10*L10*revleg_thin,0))-(((battery/range_nm)*D10*ROUND(K10*L10*revleg_thin,0)*VLOOKUP(B10,country_opex,3,FALSE))+V10+W10+X10+Y10+Z10))&lt;=0,"",VLOOKUP(B10,country_opex,7,FALSE)/((S10*pax_cap*load_thin*ROUND(K10*L10*revleg_thin,0))-(((battery/range_nm)*D10*ROUND(K10*L10*revleg_thin,0)*VLOOKUP(B10,country_opex,3,FALSE))+V10+W10+X10+Y10+Z10)))</f>
         <v/>
       </c>
-      <c r="AU10" s="43">
+      <c r="AV10" s="43">
         <f>IF(((S10*pax_cap*load_mid*ROUND(K10*L10*revleg_mid,0))-(((battery/range_nm)*D10*ROUND(K10*L10*revleg_mid,0)*VLOOKUP(B10,country_opex,3,FALSE))+V10+W10+X10+Y10+Z10))&lt;=0,"",VLOOKUP(B10,country_opex,7,FALSE)/((S10*pax_cap*load_mid*ROUND(K10*L10*revleg_mid,0))-(((battery/range_nm)*D10*ROUND(K10*L10*revleg_mid,0)*VLOOKUP(B10,country_opex,3,FALSE))+V10+W10+X10+Y10+Z10)))</f>
         <v/>
       </c>
-      <c r="AV10" s="43">
+      <c r="AW10" s="43">
         <f>IF(((S10*pax_cap*load_full*ROUND(K10*L10*revleg_full,0))-(((battery/range_nm)*D10*ROUND(K10*L10*revleg_full,0)*VLOOKUP(B10,country_opex,3,FALSE))+V10+W10+X10+Y10+Z10))&lt;=0,"",VLOOKUP(B10,country_opex,7,FALSE)/((S10*pax_cap*load_full*ROUND(K10*L10*revleg_full,0))-(((battery/range_nm)*D10*ROUND(K10*L10*revleg_full,0)*VLOOKUP(B10,country_opex,3,FALSE))+V10+W10+X10+Y10+Z10)))</f>
         <v/>
       </c>
-      <c r="AW10" s="44" t="n"/>
-      <c r="AX10" s="44" t="n"/>
+      <c r="AX10" s="44" t="inlineStr">
+        <is>
+          <t>Anantara official: day pass QAR 395/adult ($108.51) incl RT luxury catamaran transfer + QAR 345 credits. De-bundled transfer component: child rate QAR 200 RT no credits =&gt; ~QAR 100/way ~ USD 27.5/pp one-way pure-transfer value (honest band $14-55 RT).</t>
+        </is>
+      </c>
+      <c r="AY10" s="44" t="inlineStr">
+        <is>
+          <t>Anantara Banana Island official: 141 keys (anantara.com/visitqatar, T1); access is BOAT-ONLY via ~45-51-pax luxury catamaran from Al Shyoukh Terminal, 25-30 min, scheduled ~hourly 09:00-21:00 (booking.com listing; adventureparkdoha.com '45-passenger catamaran operates regularly'; observed 51-pax config). Qatar national hotel occupancy 71% 2025 (Qatar Tourism/ValuStrat, T2). Day-pass product QAR 395/adult incl. RT transfer (anantara.com, T1) adds day-tripper volume.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="29" t="inlineStr">
@@ -3510,11 +3519,11 @@
       </c>
       <c r="C11" s="30" t="inlineStr">
         <is>
-          <t>Al Wakrah → Banana Island</t>
+          <t>West Bay / Corniche (Doha) → Lusail Marina &amp; Place Vendôme</t>
         </is>
       </c>
       <c r="D11" s="31" t="n">
-        <v>9.5</v>
+        <v>6.3</v>
       </c>
       <c r="E11" s="26" t="n"/>
       <c r="F11" s="32" t="n"/>
@@ -3531,7 +3540,7 @@
         <v/>
       </c>
       <c r="K11" s="34">
-        <f>MIN(27,FLOOR(60*service_hr/J11,1))</f>
+        <f>MIN(15,FLOOR(60*service_hr/J11,1))</f>
         <v/>
       </c>
       <c r="L11" s="34">
@@ -3629,7 +3638,7 @@
         <v/>
       </c>
       <c r="AL11" s="34">
-        <f>IF(OR(AG11="",R11=0),"",MIN(IF(AS11="",9.9E+99,AS11),FLOOR(AK11/R11,1)))</f>
+        <f>IF(OR(AG11="",R11=0),"",MIN(IF(AT11="",9.9E+99,AT11),FLOOR(AK11/R11,1)))</f>
         <v/>
       </c>
       <c r="AM11" s="38">
@@ -3637,7 +3646,7 @@
         <v/>
       </c>
       <c r="AN11" s="36">
-        <f>IF(OR(AG11="",R11=0),"",MIN(IF(AS11="",9.9E+99,AS11),AK11/R11))</f>
+        <f>IF(OR(AG11="",R11=0),"",MIN(IF(AT11="",9.9E+99,AT11),AK11/R11))</f>
         <v/>
       </c>
       <c r="AO11" s="38">
@@ -3645,23 +3654,28 @@
         <v/>
       </c>
       <c r="AP11" s="40" t="n"/>
-      <c r="AQ11" s="41" t="n"/>
+      <c r="AQ11" s="32" t="inlineStr">
+        <is>
+          <t>Forward SAM</t>
+        </is>
+      </c>
       <c r="AR11" s="41" t="n"/>
-      <c r="AS11" s="42" t="n"/>
-      <c r="AT11" s="43">
+      <c r="AS11" s="41" t="n"/>
+      <c r="AT11" s="42" t="n"/>
+      <c r="AU11" s="43">
         <f>IF(((S11*pax_cap*load_thin*ROUND(K11*L11*revleg_thin,0))-(((battery/range_nm)*D11*ROUND(K11*L11*revleg_thin,0)*VLOOKUP(B11,country_opex,3,FALSE))+V11+W11+X11+Y11+Z11))&lt;=0,"",VLOOKUP(B11,country_opex,7,FALSE)/((S11*pax_cap*load_thin*ROUND(K11*L11*revleg_thin,0))-(((battery/range_nm)*D11*ROUND(K11*L11*revleg_thin,0)*VLOOKUP(B11,country_opex,3,FALSE))+V11+W11+X11+Y11+Z11)))</f>
         <v/>
       </c>
-      <c r="AU11" s="43">
+      <c r="AV11" s="43">
         <f>IF(((S11*pax_cap*load_mid*ROUND(K11*L11*revleg_mid,0))-(((battery/range_nm)*D11*ROUND(K11*L11*revleg_mid,0)*VLOOKUP(B11,country_opex,3,FALSE))+V11+W11+X11+Y11+Z11))&lt;=0,"",VLOOKUP(B11,country_opex,7,FALSE)/((S11*pax_cap*load_mid*ROUND(K11*L11*revleg_mid,0))-(((battery/range_nm)*D11*ROUND(K11*L11*revleg_mid,0)*VLOOKUP(B11,country_opex,3,FALSE))+V11+W11+X11+Y11+Z11)))</f>
         <v/>
       </c>
-      <c r="AV11" s="43">
+      <c r="AW11" s="43">
         <f>IF(((S11*pax_cap*load_full*ROUND(K11*L11*revleg_full,0))-(((battery/range_nm)*D11*ROUND(K11*L11*revleg_full,0)*VLOOKUP(B11,country_opex,3,FALSE))+V11+W11+X11+Y11+Z11))&lt;=0,"",VLOOKUP(B11,country_opex,7,FALSE)/((S11*pax_cap*load_full*ROUND(K11*L11*revleg_full,0))-(((battery/range_nm)*D11*ROUND(K11*L11*revleg_full,0)*VLOOKUP(B11,country_opex,3,FALSE))+V11+W11+X11+Y11+Z11)))</f>
         <v/>
       </c>
-      <c r="AW11" s="44" t="n"/>
       <c r="AX11" s="44" t="n"/>
+      <c r="AY11" s="44" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="29" t="inlineStr">
@@ -3676,15 +3690,25 @@
       </c>
       <c r="C12" s="30" t="inlineStr">
         <is>
-          <t>Doha → Al Wakrah Marina</t>
+          <t>West Bay / Corniche (Doha) → Lusail Marina &amp; Place Vendôme</t>
         </is>
       </c>
       <c r="D12" s="31" t="n">
-        <v>11</v>
-      </c>
-      <c r="E12" s="26" t="n"/>
-      <c r="F12" s="32" t="n"/>
-      <c r="G12" s="32" t="n"/>
+        <v>6.3</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>16</v>
+      </c>
+      <c r="F12" s="32" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="G12" s="32" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
       <c r="H12" s="19" t="n">
         <v>1</v>
       </c>
@@ -3784,9 +3808,19 @@
         <f>((D12*O12/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D12*O12*VLOOKUP(B12,country_opex,4,FALSE))/1000</f>
         <v/>
       </c>
-      <c r="AG12" s="31" t="n"/>
-      <c r="AH12" s="32" t="n"/>
-      <c r="AI12" s="32" t="n"/>
+      <c r="AG12" s="31" t="n">
+        <v>75000</v>
+      </c>
+      <c r="AH12" s="32" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="AI12" s="32" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
       <c r="AJ12" s="39" t="n">
         <v>0.1</v>
       </c>
@@ -3795,7 +3829,7 @@
         <v/>
       </c>
       <c r="AL12" s="34">
-        <f>IF(OR(AG12="",R12=0),"",MIN(IF(AS12="",9.9E+99,AS12),FLOOR(AK12/R12,1)))</f>
+        <f>IF(OR(AG12="",R12=0),"",MIN(IF(AT12="",9.9E+99,AT12),FLOOR(AK12/R12,1)))</f>
         <v/>
       </c>
       <c r="AM12" s="38">
@@ -3803,7 +3837,7 @@
         <v/>
       </c>
       <c r="AN12" s="36">
-        <f>IF(OR(AG12="",R12=0),"",MIN(IF(AS12="",9.9E+99,AS12),AK12/R12))</f>
+        <f>IF(OR(AG12="",R12=0),"",MIN(IF(AT12="",9.9E+99,AT12),AK12/R12))</f>
         <v/>
       </c>
       <c r="AO12" s="38">
@@ -3811,147 +3845,699 @@
         <v/>
       </c>
       <c r="AP12" s="40" t="n"/>
-      <c r="AQ12" s="41" t="n"/>
-      <c r="AR12" s="41" t="n"/>
-      <c r="AS12" s="42" t="n"/>
-      <c r="AT12" s="43">
+      <c r="AQ12" s="32" t="inlineStr">
+        <is>
+          <t>Forward SAM</t>
+        </is>
+      </c>
+      <c r="AR12" s="41" t="inlineStr">
+        <is>
+          <t>FWD-SAM (2030)</t>
+        </is>
+      </c>
+      <c r="AS12" s="41" t="n"/>
+      <c r="AT12" s="42" t="n"/>
+      <c r="AU12" s="43">
         <f>IF(((S12*pax_cap*load_thin*ROUND(K12*L12*revleg_thin,0))-(((battery/range_nm)*D12*ROUND(K12*L12*revleg_thin,0)*VLOOKUP(B12,country_opex,3,FALSE))+V12+W12+X12+Y12+Z12))&lt;=0,"",VLOOKUP(B12,country_opex,7,FALSE)/((S12*pax_cap*load_thin*ROUND(K12*L12*revleg_thin,0))-(((battery/range_nm)*D12*ROUND(K12*L12*revleg_thin,0)*VLOOKUP(B12,country_opex,3,FALSE))+V12+W12+X12+Y12+Z12)))</f>
         <v/>
       </c>
-      <c r="AU12" s="43">
+      <c r="AV12" s="43">
         <f>IF(((S12*pax_cap*load_mid*ROUND(K12*L12*revleg_mid,0))-(((battery/range_nm)*D12*ROUND(K12*L12*revleg_mid,0)*VLOOKUP(B12,country_opex,3,FALSE))+V12+W12+X12+Y12+Z12))&lt;=0,"",VLOOKUP(B12,country_opex,7,FALSE)/((S12*pax_cap*load_mid*ROUND(K12*L12*revleg_mid,0))-(((battery/range_nm)*D12*ROUND(K12*L12*revleg_mid,0)*VLOOKUP(B12,country_opex,3,FALSE))+V12+W12+X12+Y12+Z12)))</f>
         <v/>
       </c>
-      <c r="AV12" s="43">
+      <c r="AW12" s="43">
         <f>IF(((S12*pax_cap*load_full*ROUND(K12*L12*revleg_full,0))-(((battery/range_nm)*D12*ROUND(K12*L12*revleg_full,0)*VLOOKUP(B12,country_opex,3,FALSE))+V12+W12+X12+Y12+Z12))&lt;=0,"",VLOOKUP(B12,country_opex,7,FALSE)/((S12*pax_cap*load_full*ROUND(K12*L12*revleg_full,0))-(((battery/range_nm)*D12*ROUND(K12*L12*revleg_full,0)*VLOOKUP(B12,country_opex,3,FALSE))+V12+W12+X12+Y12+Z12)))</f>
         <v/>
       </c>
-      <c r="AW12" s="44" t="n"/>
-      <c r="AX12" s="44" t="n"/>
+      <c r="AX12" s="44" t="inlineStr">
+        <is>
+          <t>No scheduled service yet: MOT Water Taxi Phase-1 INFRASTRUCTURE complete 7 Nov 2024 (Lusail Ferry Terminal + Pearl &amp; Corniche stops, EV-charger-fitted) but operator unselected, no fare published (mot.gov.qa). Cascaded from on-network premium per-seat anchor Ronautica Pearl gate-to-gate QAR 40/pp (USD 10.99) scaled per-nm 4.4-&gt;6.3nm =&gt; ~$15.7. Leisure upper bound: Blue Pearl shared speedboat West Bay QAR 160/pp ($43.95).</t>
+        </is>
+      </c>
+      <c r="AY12" s="44" t="inlineStr">
+        <is>
+          <t>No marine service operates on this corridor today (greenfield; MOT Water Taxi Phase-1 INFRASTRUCTURE complete Nov-2024 — Lusail Ferry Terminal + Corniche Ferry Stop sit EXACTLY on this corridor's endpoints, with electric-ferry chargers — but operator not yet selected; network capacity unpublished, mot.gov.qa). Destination pools (all LAND-arriving, R3-LAND caveat): Al Maha Island Lusail target 1.5M visitors/yr (Gulf Times/developer); Place Vendome mall claims 16.5M annual footfall (UDC leasing brochure 2025, marketing-grade); Lusail Boulevard 250k visitors on NYE 2025 alone (wgoqatar); Doha Corniche promenade has NO published count. Qatar 5.08M intl visitors 2024 / 5.1M 2025 (Qatar Tourism, T1).</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="45" t="inlineStr">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="B13" s="29" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="C13" s="30" t="inlineStr">
+        <is>
+          <t>Doha → Lusail Marina</t>
+        </is>
+      </c>
+      <c r="D13" s="31" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E13" s="26" t="n"/>
+      <c r="F13" s="32" t="n"/>
+      <c r="G13" s="32" t="n"/>
+      <c r="H13" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="33">
+        <f>60*D13/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J13" s="33">
+        <f>I13+turn_min+dwell_min</f>
+        <v/>
+      </c>
+      <c r="K13" s="34">
+        <f>MIN(27,FLOOR(60*service_hr/J13,1))</f>
+        <v/>
+      </c>
+      <c r="L13" s="34">
+        <f>ROUND(365*mech_uptime*H13,0)</f>
+        <v/>
+      </c>
+      <c r="M13" s="35">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="N13" s="35">
+        <f>revleg_sel</f>
+        <v/>
+      </c>
+      <c r="O13" s="34">
+        <f>ROUND(K13*L13*revleg_sel,0)</f>
+        <v/>
+      </c>
+      <c r="P13" s="36">
+        <f>load_sel</f>
+        <v/>
+      </c>
+      <c r="Q13" s="36">
+        <f>pax_cap*P13</f>
+        <v/>
+      </c>
+      <c r="R13" s="34">
+        <f>Q13*O13</f>
+        <v/>
+      </c>
+      <c r="S13" s="37">
+        <f>E13*discount</f>
+        <v/>
+      </c>
+      <c r="T13" s="38">
+        <f>S13*R13</f>
+        <v/>
+      </c>
+      <c r="U13" s="38">
+        <f>(battery/range_nm)*D13*O13*VLOOKUP(B13,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="V13" s="38">
+        <f>VLOOKUP(B13,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="W13" s="38">
+        <f>VLOOKUP(B13,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="X13" s="38">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Y13" s="38">
+        <f>VLOOKUP(B13,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="Z13" s="38">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AA13" s="38">
+        <f>U13+V13+W13+X13+Y13+Z13</f>
+        <v/>
+      </c>
+      <c r="AB13" s="38">
+        <f>VLOOKUP(B13,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AC13" s="38">
+        <f>T13-AA13</f>
+        <v/>
+      </c>
+      <c r="AD13" s="35">
+        <f>IF(T13=0,"",AC13/T13)</f>
+        <v/>
+      </c>
+      <c r="AE13" s="36">
+        <f>IF(AC13&lt;=0,"",VLOOKUP(B13,country_opex,7,FALSE)/AC13)</f>
+        <v/>
+      </c>
+      <c r="AF13" s="33">
+        <f>((D13*O13/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D13*O13*VLOOKUP(B13,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AG13" s="31" t="n"/>
+      <c r="AH13" s="32" t="n"/>
+      <c r="AI13" s="32" t="n"/>
+      <c r="AJ13" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK13" s="34">
+        <f>IF(AG13="","",AG13*AJ13)</f>
+        <v/>
+      </c>
+      <c r="AL13" s="34">
+        <f>IF(OR(AG13="",R13=0),"",MIN(IF(AT13="",9.9E+99,AT13),FLOOR(AK13/R13,1)))</f>
+        <v/>
+      </c>
+      <c r="AM13" s="38">
+        <f>IF(AL13="","",AL13*T13)</f>
+        <v/>
+      </c>
+      <c r="AN13" s="36">
+        <f>IF(OR(AG13="",R13=0),"",MIN(IF(AT13="",9.9E+99,AT13),AK13/R13))</f>
+        <v/>
+      </c>
+      <c r="AO13" s="38">
+        <f>IF(AN13="","",AN13*T13)</f>
+        <v/>
+      </c>
+      <c r="AP13" s="40" t="n"/>
+      <c r="AQ13" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+      <c r="AR13" s="41" t="n"/>
+      <c r="AS13" s="41" t="n"/>
+      <c r="AT13" s="42" t="n"/>
+      <c r="AU13" s="43">
+        <f>IF(((S13*pax_cap*load_thin*ROUND(K13*L13*revleg_thin,0))-(((battery/range_nm)*D13*ROUND(K13*L13*revleg_thin,0)*VLOOKUP(B13,country_opex,3,FALSE))+V13+W13+X13+Y13+Z13))&lt;=0,"",VLOOKUP(B13,country_opex,7,FALSE)/((S13*pax_cap*load_thin*ROUND(K13*L13*revleg_thin,0))-(((battery/range_nm)*D13*ROUND(K13*L13*revleg_thin,0)*VLOOKUP(B13,country_opex,3,FALSE))+V13+W13+X13+Y13+Z13)))</f>
+        <v/>
+      </c>
+      <c r="AV13" s="43">
+        <f>IF(((S13*pax_cap*load_mid*ROUND(K13*L13*revleg_mid,0))-(((battery/range_nm)*D13*ROUND(K13*L13*revleg_mid,0)*VLOOKUP(B13,country_opex,3,FALSE))+V13+W13+X13+Y13+Z13))&lt;=0,"",VLOOKUP(B13,country_opex,7,FALSE)/((S13*pax_cap*load_mid*ROUND(K13*L13*revleg_mid,0))-(((battery/range_nm)*D13*ROUND(K13*L13*revleg_mid,0)*VLOOKUP(B13,country_opex,3,FALSE))+V13+W13+X13+Y13+Z13)))</f>
+        <v/>
+      </c>
+      <c r="AW13" s="43">
+        <f>IF(((S13*pax_cap*load_full*ROUND(K13*L13*revleg_full,0))-(((battery/range_nm)*D13*ROUND(K13*L13*revleg_full,0)*VLOOKUP(B13,country_opex,3,FALSE))+V13+W13+X13+Y13+Z13))&lt;=0,"",VLOOKUP(B13,country_opex,7,FALSE)/((S13*pax_cap*load_full*ROUND(K13*L13*revleg_full,0))-(((battery/range_nm)*D13*ROUND(K13*L13*revleg_full,0)*VLOOKUP(B13,country_opex,3,FALSE))+V13+W13+X13+Y13+Z13)))</f>
+        <v/>
+      </c>
+      <c r="AX13" s="44" t="n"/>
+      <c r="AY13" s="44" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="B14" s="29" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="C14" s="30" t="inlineStr">
+        <is>
+          <t>Al Wakrah → Banana Island</t>
+        </is>
+      </c>
+      <c r="D14" s="31" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E14" s="26" t="n"/>
+      <c r="F14" s="32" t="n"/>
+      <c r="G14" s="32" t="n"/>
+      <c r="H14" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="33">
+        <f>60*D14/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J14" s="33">
+        <f>I14+turn_min+dwell_min</f>
+        <v/>
+      </c>
+      <c r="K14" s="34">
+        <f>MIN(27,FLOOR(60*service_hr/J14,1))</f>
+        <v/>
+      </c>
+      <c r="L14" s="34">
+        <f>ROUND(365*mech_uptime*H14,0)</f>
+        <v/>
+      </c>
+      <c r="M14" s="35">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="N14" s="35">
+        <f>revleg_sel</f>
+        <v/>
+      </c>
+      <c r="O14" s="34">
+        <f>ROUND(K14*L14*revleg_sel,0)</f>
+        <v/>
+      </c>
+      <c r="P14" s="36">
+        <f>load_sel</f>
+        <v/>
+      </c>
+      <c r="Q14" s="36">
+        <f>pax_cap*P14</f>
+        <v/>
+      </c>
+      <c r="R14" s="34">
+        <f>Q14*O14</f>
+        <v/>
+      </c>
+      <c r="S14" s="37">
+        <f>E14*discount</f>
+        <v/>
+      </c>
+      <c r="T14" s="38">
+        <f>S14*R14</f>
+        <v/>
+      </c>
+      <c r="U14" s="38">
+        <f>(battery/range_nm)*D14*O14*VLOOKUP(B14,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="V14" s="38">
+        <f>VLOOKUP(B14,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="W14" s="38">
+        <f>VLOOKUP(B14,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="X14" s="38">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Y14" s="38">
+        <f>VLOOKUP(B14,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="Z14" s="38">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AA14" s="38">
+        <f>U14+V14+W14+X14+Y14+Z14</f>
+        <v/>
+      </c>
+      <c r="AB14" s="38">
+        <f>VLOOKUP(B14,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AC14" s="38">
+        <f>T14-AA14</f>
+        <v/>
+      </c>
+      <c r="AD14" s="35">
+        <f>IF(T14=0,"",AC14/T14)</f>
+        <v/>
+      </c>
+      <c r="AE14" s="36">
+        <f>IF(AC14&lt;=0,"",VLOOKUP(B14,country_opex,7,FALSE)/AC14)</f>
+        <v/>
+      </c>
+      <c r="AF14" s="33">
+        <f>((D14*O14/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D14*O14*VLOOKUP(B14,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AG14" s="31" t="n"/>
+      <c r="AH14" s="32" t="n"/>
+      <c r="AI14" s="32" t="n"/>
+      <c r="AJ14" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK14" s="34">
+        <f>IF(AG14="","",AG14*AJ14)</f>
+        <v/>
+      </c>
+      <c r="AL14" s="34">
+        <f>IF(OR(AG14="",R14=0),"",MIN(IF(AT14="",9.9E+99,AT14),FLOOR(AK14/R14,1)))</f>
+        <v/>
+      </c>
+      <c r="AM14" s="38">
+        <f>IF(AL14="","",AL14*T14)</f>
+        <v/>
+      </c>
+      <c r="AN14" s="36">
+        <f>IF(OR(AG14="",R14=0),"",MIN(IF(AT14="",9.9E+99,AT14),AK14/R14))</f>
+        <v/>
+      </c>
+      <c r="AO14" s="38">
+        <f>IF(AN14="","",AN14*T14)</f>
+        <v/>
+      </c>
+      <c r="AP14" s="40" t="n"/>
+      <c r="AQ14" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+      <c r="AR14" s="41" t="n"/>
+      <c r="AS14" s="41" t="n"/>
+      <c r="AT14" s="42" t="n"/>
+      <c r="AU14" s="43">
+        <f>IF(((S14*pax_cap*load_thin*ROUND(K14*L14*revleg_thin,0))-(((battery/range_nm)*D14*ROUND(K14*L14*revleg_thin,0)*VLOOKUP(B14,country_opex,3,FALSE))+V14+W14+X14+Y14+Z14))&lt;=0,"",VLOOKUP(B14,country_opex,7,FALSE)/((S14*pax_cap*load_thin*ROUND(K14*L14*revleg_thin,0))-(((battery/range_nm)*D14*ROUND(K14*L14*revleg_thin,0)*VLOOKUP(B14,country_opex,3,FALSE))+V14+W14+X14+Y14+Z14)))</f>
+        <v/>
+      </c>
+      <c r="AV14" s="43">
+        <f>IF(((S14*pax_cap*load_mid*ROUND(K14*L14*revleg_mid,0))-(((battery/range_nm)*D14*ROUND(K14*L14*revleg_mid,0)*VLOOKUP(B14,country_opex,3,FALSE))+V14+W14+X14+Y14+Z14))&lt;=0,"",VLOOKUP(B14,country_opex,7,FALSE)/((S14*pax_cap*load_mid*ROUND(K14*L14*revleg_mid,0))-(((battery/range_nm)*D14*ROUND(K14*L14*revleg_mid,0)*VLOOKUP(B14,country_opex,3,FALSE))+V14+W14+X14+Y14+Z14)))</f>
+        <v/>
+      </c>
+      <c r="AW14" s="43">
+        <f>IF(((S14*pax_cap*load_full*ROUND(K14*L14*revleg_full,0))-(((battery/range_nm)*D14*ROUND(K14*L14*revleg_full,0)*VLOOKUP(B14,country_opex,3,FALSE))+V14+W14+X14+Y14+Z14))&lt;=0,"",VLOOKUP(B14,country_opex,7,FALSE)/((S14*pax_cap*load_full*ROUND(K14*L14*revleg_full,0))-(((battery/range_nm)*D14*ROUND(K14*L14*revleg_full,0)*VLOOKUP(B14,country_opex,3,FALSE))+V14+W14+X14+Y14+Z14)))</f>
+        <v/>
+      </c>
+      <c r="AX14" s="44" t="n"/>
+      <c r="AY14" s="44" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="29" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="B15" s="29" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="C15" s="30" t="inlineStr">
+        <is>
+          <t>Doha → Al Wakrah Marina</t>
+        </is>
+      </c>
+      <c r="D15" s="31" t="n">
+        <v>11</v>
+      </c>
+      <c r="E15" s="26" t="n"/>
+      <c r="F15" s="32" t="n"/>
+      <c r="G15" s="32" t="n"/>
+      <c r="H15" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="33">
+        <f>60*D15/cruise_kt</f>
+        <v/>
+      </c>
+      <c r="J15" s="33">
+        <f>I15+turn_min+dwell_min</f>
+        <v/>
+      </c>
+      <c r="K15" s="34">
+        <f>MIN(27,FLOOR(60*service_hr/J15,1))</f>
+        <v/>
+      </c>
+      <c r="L15" s="34">
+        <f>ROUND(365*mech_uptime*H15,0)</f>
+        <v/>
+      </c>
+      <c r="M15" s="35">
+        <f>mech_uptime</f>
+        <v/>
+      </c>
+      <c r="N15" s="35">
+        <f>revleg_sel</f>
+        <v/>
+      </c>
+      <c r="O15" s="34">
+        <f>ROUND(K15*L15*revleg_sel,0)</f>
+        <v/>
+      </c>
+      <c r="P15" s="36">
+        <f>load_sel</f>
+        <v/>
+      </c>
+      <c r="Q15" s="36">
+        <f>pax_cap*P15</f>
+        <v/>
+      </c>
+      <c r="R15" s="34">
+        <f>Q15*O15</f>
+        <v/>
+      </c>
+      <c r="S15" s="37">
+        <f>E15*discount</f>
+        <v/>
+      </c>
+      <c r="T15" s="38">
+        <f>S15*R15</f>
+        <v/>
+      </c>
+      <c r="U15" s="38">
+        <f>(battery/range_nm)*D15*O15*VLOOKUP(B15,country_opex,3,FALSE)</f>
+        <v/>
+      </c>
+      <c r="V15" s="38">
+        <f>VLOOKUP(B15,country_opex,2,FALSE)*crew_factor</f>
+        <v/>
+      </c>
+      <c r="W15" s="38">
+        <f>VLOOKUP(B15,country_opex,5,FALSE)</f>
+        <v/>
+      </c>
+      <c r="X15" s="38">
+        <f>maint</f>
+        <v/>
+      </c>
+      <c r="Y15" s="38">
+        <f>VLOOKUP(B15,country_opex,7,FALSE)*ins_pct</f>
+        <v/>
+      </c>
+      <c r="Z15" s="38">
+        <f>charge_berth</f>
+        <v/>
+      </c>
+      <c r="AA15" s="38">
+        <f>U15+V15+W15+X15+Y15+Z15</f>
+        <v/>
+      </c>
+      <c r="AB15" s="38">
+        <f>VLOOKUP(B15,country_opex,7,FALSE)/dep_years</f>
+        <v/>
+      </c>
+      <c r="AC15" s="38">
+        <f>T15-AA15</f>
+        <v/>
+      </c>
+      <c r="AD15" s="35">
+        <f>IF(T15=0,"",AC15/T15)</f>
+        <v/>
+      </c>
+      <c r="AE15" s="36">
+        <f>IF(AC15&lt;=0,"",VLOOKUP(B15,country_opex,7,FALSE)/AC15)</f>
+        <v/>
+      </c>
+      <c r="AF15" s="33">
+        <f>((D15*O15/diesel_nmpg)*diesel_co2pg-(battery/range_nm)*D15*O15*VLOOKUP(B15,country_opex,4,FALSE))/1000</f>
+        <v/>
+      </c>
+      <c r="AG15" s="31" t="n"/>
+      <c r="AH15" s="32" t="n"/>
+      <c r="AI15" s="32" t="n"/>
+      <c r="AJ15" s="39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK15" s="34">
+        <f>IF(AG15="","",AG15*AJ15)</f>
+        <v/>
+      </c>
+      <c r="AL15" s="34">
+        <f>IF(OR(AG15="",R15=0),"",MIN(IF(AT15="",9.9E+99,AT15),FLOOR(AK15/R15,1)))</f>
+        <v/>
+      </c>
+      <c r="AM15" s="38">
+        <f>IF(AL15="","",AL15*T15)</f>
+        <v/>
+      </c>
+      <c r="AN15" s="36">
+        <f>IF(OR(AG15="",R15=0),"",MIN(IF(AT15="",9.9E+99,AT15),AK15/R15))</f>
+        <v/>
+      </c>
+      <c r="AO15" s="38">
+        <f>IF(AN15="","",AN15*T15)</f>
+        <v/>
+      </c>
+      <c r="AP15" s="40" t="n"/>
+      <c r="AQ15" s="32" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+      <c r="AR15" s="41" t="n"/>
+      <c r="AS15" s="41" t="n"/>
+      <c r="AT15" s="42" t="n"/>
+      <c r="AU15" s="43">
+        <f>IF(((S15*pax_cap*load_thin*ROUND(K15*L15*revleg_thin,0))-(((battery/range_nm)*D15*ROUND(K15*L15*revleg_thin,0)*VLOOKUP(B15,country_opex,3,FALSE))+V15+W15+X15+Y15+Z15))&lt;=0,"",VLOOKUP(B15,country_opex,7,FALSE)/((S15*pax_cap*load_thin*ROUND(K15*L15*revleg_thin,0))-(((battery/range_nm)*D15*ROUND(K15*L15*revleg_thin,0)*VLOOKUP(B15,country_opex,3,FALSE))+V15+W15+X15+Y15+Z15)))</f>
+        <v/>
+      </c>
+      <c r="AV15" s="43">
+        <f>IF(((S15*pax_cap*load_mid*ROUND(K15*L15*revleg_mid,0))-(((battery/range_nm)*D15*ROUND(K15*L15*revleg_mid,0)*VLOOKUP(B15,country_opex,3,FALSE))+V15+W15+X15+Y15+Z15))&lt;=0,"",VLOOKUP(B15,country_opex,7,FALSE)/((S15*pax_cap*load_mid*ROUND(K15*L15*revleg_mid,0))-(((battery/range_nm)*D15*ROUND(K15*L15*revleg_mid,0)*VLOOKUP(B15,country_opex,3,FALSE))+V15+W15+X15+Y15+Z15)))</f>
+        <v/>
+      </c>
+      <c r="AW15" s="43">
+        <f>IF(((S15*pax_cap*load_full*ROUND(K15*L15*revleg_full,0))-(((battery/range_nm)*D15*ROUND(K15*L15*revleg_full,0)*VLOOKUP(B15,country_opex,3,FALSE))+V15+W15+X15+Y15+Z15))&lt;=0,"",VLOOKUP(B15,country_opex,7,FALSE)/((S15*pax_cap*load_full*ROUND(K15*L15*revleg_full,0))-(((battery/range_nm)*D15*ROUND(K15*L15*revleg_full,0)*VLOOKUP(B15,country_opex,3,FALSE))+V15+W15+X15+Y15+Z15)))</f>
+        <v/>
+      </c>
+      <c r="AX15" s="44" t="n"/>
+      <c r="AY15" s="44" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="45" t="inlineStr">
         <is>
           <t>TOTAL / median</t>
         </is>
       </c>
-      <c r="T13" s="46">
-        <f>SUM(T4:T12)</f>
-        <v/>
-      </c>
-      <c r="AC13" s="46">
-        <f>SUM(AC4:AC12)</f>
-        <v/>
-      </c>
-      <c r="AD13" s="47">
-        <f>IF(T13=0,"",AC13/T13)</f>
-        <v/>
-      </c>
-      <c r="AL13" s="48">
-        <f>SUM(AL4:AL12)</f>
-        <v/>
-      </c>
-      <c r="AM13" s="46">
-        <f>SUM(AM4:AM12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="T16" s="46">
+        <f>SUM(T4:T15)</f>
+        <v/>
+      </c>
+      <c r="AC16" s="46">
+        <f>SUM(AC4:AC15)</f>
+        <v/>
+      </c>
+      <c r="AD16" s="47">
+        <f>IF(T16=0,"",AC16/T16)</f>
+        <v/>
+      </c>
+      <c r="AL16" s="48">
+        <f>SUM(AL4:AL15)</f>
+        <v/>
+      </c>
+      <c r="AM16" s="46">
+        <f>SUM(AM4:AM15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>Market fleet build-up — grounded floor (network-sum of raw vessel fractions per market, rounded once; subset slices excluded; legacy per-corridor-floor totals above kept for reference)</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="24" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="24" t="inlineStr">
         <is>
           <t>Market</t>
         </is>
       </c>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>Fleet basis</t>
         </is>
       </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>Raw vessels (sum)</t>
         </is>
       </c>
-      <c r="D16" s="24" t="inlineStr">
+      <c r="D19" s="24" t="inlineStr">
         <is>
           <t>Fleet (rounded once)</t>
         </is>
       </c>
-      <c r="E16" s="24" t="inlineStr">
+      <c r="E19" s="24" t="inlineStr">
         <is>
           <t>Market rev/yr (raw sum)</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="25" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="25" t="inlineStr">
         <is>
           <t>Qatar</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>per_corridor_floor</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D17" s="49">
-        <f>SUMIFS(AL4:AL12,A4:A12,"Qatar",AP4:AP12,"=",AQ4:AQ12,"=",AR4:AR12,"=")</f>
-        <v/>
-      </c>
-      <c r="E17" s="50">
-        <f>SUMIFS(AM4:AM12,A4:A12,"Qatar",AP4:AP12,"=",AQ4:AQ12,"=",AR4:AR12,"=")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="45" t="inlineStr">
+      <c r="D20" s="49">
+        <f>SUMIFS(AL4:AL15,A4:A15,"Qatar",AP4:AP15,"=",AQ4:AQ15,"Grounded")</f>
+        <v/>
+      </c>
+      <c r="E20" s="50">
+        <f>SUMIFS(AM4:AM15,A4:A15,"Qatar",AP4:AP15,"=",AQ4:AQ15,"Grounded")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="45" t="inlineStr">
         <is>
           <t>GROUNDED FLOOR (PUBLISHED)</t>
         </is>
       </c>
-      <c r="D18" s="48">
-        <f>SUM(D17:D17)</f>
-        <v/>
-      </c>
-      <c r="E18" s="46">
-        <f>SUM(E17:E17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="D21" s="48">
+        <f>SUM(D20:D20)</f>
+        <v/>
+      </c>
+      <c r="E21" s="46">
+        <f>SUM(E20:E20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t>ESTIMATED DEMAND (country-median cascade; held OUT of grounded floor)</t>
+        </is>
+      </c>
+      <c r="D22" s="51">
+        <f>SUMIF(AQ4:AQ15,"Estimated",AL4:AL15)</f>
+        <v/>
+      </c>
+      <c r="E22" s="52">
+        <f>SUMIF(AQ4:AQ15,"Estimated",AM4:AM15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>FORWARD SAM (2030-dated; held OUT of grounded floor)</t>
         </is>
       </c>
-      <c r="D19" s="51">
-        <f>SUMIF(AQ4:AQ12,"&lt;&gt;",AL4:AL12)</f>
-        <v/>
-      </c>
-      <c r="E19" s="52">
-        <f>SUMIF(AQ4:AQ12,"&lt;&gt;",AM4:AM12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="53" t="inlineStr">
+      <c r="D23" s="51">
+        <f>SUMIF(AQ4:AQ15,"Forward SAM",AL4:AL15)</f>
+        <v/>
+      </c>
+      <c r="E23" s="52">
+        <f>SUMIF(AQ4:AQ15,"Forward SAM",AM4:AM15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="53" t="inlineStr">
         <is>
           <t>Held for Quanta-LR (&gt;70nm, roadmap H2 2026+):</t>
         </is>
       </c>
-      <c r="C21" s="54" t="inlineStr">
+      <c r="C25" s="54" t="inlineStr">
+        <is>
+          <t>Doha (Lusail Marina) → Manama (Bahrain Financial Harbour) (94.5nm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" s="54" t="inlineStr">
         <is>
           <t>Doha (Lusail Marina) → Manama (Bahrain Financial Harbour) (94.5nm)</t>
         </is>
@@ -3959,8 +4545,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A15:L15"/>
     <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A18:L18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4183,7 +4769,7 @@
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Live sum of grounded corridor market-rev (10% capture, today's demand, sourced corridors).</t>
+          <t>Live sum of grounded-floor corridor market-rev only (Floor bucket = Grounded; cascade-estimated rows held out). Matches growth.py _headline_anchor and deck TAM.</t>
         </is>
       </c>
     </row>
